--- a/panchang-data/Chennai2026.xlsx
+++ b/panchang-data/Chennai2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5371">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16138,6 +16138,9 @@
   </si>
   <si>
     <t>121°05'08.92</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16627,7 +16630,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16713,7 +16716,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16799,7 +16802,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16885,7 +16888,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -16971,7 +16974,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17057,7 +17060,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17143,7 +17146,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17229,7 +17232,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17315,7 +17318,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17401,7 +17404,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17487,7 +17490,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17573,7 +17576,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17659,7 +17662,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17745,7 +17748,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17831,7 +17834,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17917,7 +17920,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18003,7 +18006,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18089,7 +18092,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18175,7 +18178,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18261,7 +18264,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18347,7 +18350,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18433,7 +18436,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18519,7 +18522,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18605,7 +18608,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18691,7 +18694,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18777,7 +18780,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18863,7 +18866,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -18949,7 +18952,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19035,7 +19038,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19121,7 +19124,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19207,7 +19210,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19293,7 +19296,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19379,7 +19382,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19465,7 +19468,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19551,7 +19554,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19637,7 +19640,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19723,7 +19726,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19809,7 +19812,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19895,7 +19898,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -19981,7 +19984,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20067,7 +20070,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20153,7 +20156,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20239,7 +20242,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20325,7 +20328,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20411,7 +20414,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20497,7 +20500,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20583,7 +20586,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20669,7 +20672,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20755,7 +20758,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20841,7 +20844,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20927,7 +20930,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21013,7 +21016,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21099,7 +21102,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21185,7 +21188,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21271,7 +21274,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21357,7 +21360,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21443,7 +21446,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21529,7 +21532,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21615,7 +21618,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21701,7 +21704,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21787,7 +21790,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21873,7 +21876,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>563</v>
+        <v>1000</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -21959,7 +21962,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22045,7 +22048,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22131,7 +22134,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22217,7 +22220,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22303,7 +22306,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22389,7 +22392,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22475,7 +22478,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22561,7 +22564,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22647,7 +22650,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22733,7 +22736,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22819,7 +22822,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22905,7 +22908,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -22991,7 +22994,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23077,7 +23080,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23163,7 +23166,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23249,7 +23252,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23335,7 +23338,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23421,7 +23424,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23507,7 +23510,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23593,7 +23596,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23679,7 +23682,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23765,7 +23768,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23851,7 +23854,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23937,7 +23940,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24023,7 +24026,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24109,7 +24112,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24195,7 +24198,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24281,7 +24284,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24367,7 +24370,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24453,7 +24456,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24539,7 +24542,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24625,7 +24628,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24711,7 +24714,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24797,7 +24800,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24883,7 +24886,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -24969,7 +24972,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25055,7 +25058,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25141,7 +25144,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25227,7 +25230,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25313,7 +25316,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25399,7 +25402,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25485,7 +25488,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25571,7 +25574,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25657,7 +25660,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25743,7 +25746,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25829,7 +25832,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25915,7 +25918,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26001,7 +26004,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26087,7 +26090,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26173,7 +26176,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26259,7 +26262,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26345,7 +26348,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26431,7 +26434,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26517,7 +26520,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26603,7 +26606,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26689,7 +26692,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26775,7 +26778,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26861,7 +26864,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26947,7 +26950,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1441</v>
+        <v>1865</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27033,7 +27036,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27119,7 +27122,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27205,7 +27208,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27291,7 +27294,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27377,7 +27380,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27463,7 +27466,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27549,7 +27552,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27635,7 +27638,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27721,7 +27724,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27807,7 +27810,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27893,7 +27896,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -27979,7 +27982,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28065,7 +28068,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28151,7 +28154,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28237,7 +28240,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1865</v>
+        <v>2302</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28323,7 +28326,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28409,7 +28412,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28495,7 +28498,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28581,7 +28584,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28667,7 +28670,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28753,7 +28756,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28839,7 +28842,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28925,7 +28928,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29011,7 +29014,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29097,7 +29100,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29183,7 +29186,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29269,7 +29272,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29355,7 +29358,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29441,7 +29444,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29527,7 +29530,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1865</v>
+        <v>5370</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29613,7 +29616,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29699,7 +29702,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29785,7 +29788,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29871,7 +29874,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -29957,7 +29960,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30043,7 +30046,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30129,7 +30132,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30215,7 +30218,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30301,7 +30304,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30387,7 +30390,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30473,7 +30476,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30559,7 +30562,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30645,7 +30648,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30731,7 +30734,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30817,7 +30820,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2302</v>
+        <v>5370</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
